--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484083_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484083_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6326</v>
+        <v>3.348</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4883</v>
+        <v>2.2994</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1442</v>
+        <v>1.0486</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6667</v>
+        <v>4.8191</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.756</v>
+        <v>2.3432</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4227</v>
+        <v>2.4759</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4705</v>
+        <v>3.4278</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.382</v>
+        <v>2.1828</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8525</v>
+        <v>1.245</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1962</v>
+        <v>1.3913</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3739</v>
+        <v>0.1605</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5702</v>
+        <v>1.2309</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.9838</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9758</v>
+        <v>-1.1903</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1995</v>
+        <v>-0.2013</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3742</v>
+        <v>-0.204</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1747</v>
+        <v>0.0027</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7502</v>
+        <v>-0.873</v>
       </c>
       <c r="W2" t="n">
-        <v>3.6194</v>
+        <v>0.266</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8692</v>
+        <v>-1.139</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.597</v>
+        <v>2.2573</v>
       </c>
       <c r="E3" t="n">
-        <v>1.829</v>
+        <v>2.0009</v>
       </c>
       <c r="F3" t="n">
-        <v>0.768</v>
+        <v>0.2565</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8191</v>
+        <v>1.6667</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3432</v>
+        <v>-0.756</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4759</v>
+        <v>2.4227</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4278</v>
+        <v>1.4705</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1828</v>
+        <v>-0.382</v>
       </c>
       <c r="L3" t="n">
-        <v>1.245</v>
+        <v>1.8525</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3913</v>
+        <v>0.1962</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1605</v>
+        <v>-0.3739</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2309</v>
+        <v>0.5702</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3968</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1903</v>
+        <v>-2.9758</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9523</v>
+        <v>-0.1758</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6744</v>
+        <v>-0.1133</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2778</v>
+        <v>-0.0625</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.873</v>
+        <v>2.7502</v>
       </c>
       <c r="W3" t="n">
-        <v>0.266</v>
+        <v>3.6194</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.139</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8831</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3879</v>
+        <v>1.1442</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5416</v>
+        <v>-0.261</v>
       </c>
       <c r="G4" t="n">
         <v>-0.259</v>
@@ -766,13 +766,13 @@
         <v>0.5952</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1643</v>
+        <v>-0.1275</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0056</v>
+        <v>-0.2493</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1587</v>
+        <v>0.1218</v>
       </c>
       <c r="V4" t="n">
         <v>0.6745</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. RIOS CADENAS</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6256</v>
+        <v>-0.8465</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6503</v>
+        <v>-1.8387</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0248</v>
+        <v>0.9922</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7659</v>
+        <v>-2.0912</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7634</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9975000000000001</v>
+        <v>-1.3397</v>
       </c>
       <c r="J5" t="n">
-        <v>0.259</v>
+        <v>-2.1156</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.311</v>
+        <v>0.0403</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5699</v>
+        <v>-2.156</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0248</v>
+        <v>0.0244</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4525</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4276</v>
+        <v>0.8162</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.9758</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.1661</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1037</v>
+        <v>-0.2395</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3119</v>
+        <v>0.0624</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2081</v>
+        <v>-0.3019</v>
       </c>
       <c r="V5" t="n">
-        <v>3.0123</v>
+        <v>1.881</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9449</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0675</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. NDOUR</t>
+          <t>P. RIOS CADENAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.002</v>
+        <v>-0.8809</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6717</v>
+        <v>-0.9338</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3303</v>
+        <v>0.0528</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9564</v>
+        <v>-0.7659</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0155</v>
+        <v>-1.7634</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9719</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9303</v>
+        <v>0.259</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6452</v>
+        <v>-0.311</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2852</v>
+        <v>0.5699</v>
       </c>
       <c r="M6" t="n">
-        <v>0.026</v>
+        <v>-1.0248</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6607</v>
+        <v>-1.4525</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6867</v>
+        <v>0.4276</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.7774</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1741</v>
+        <v>-4.1661</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6919999999999999</v>
+        <v>-0.1516</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3061</v>
+        <v>0.0284</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3859</v>
+        <v>-0.1801</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.873</v>
+        <v>3.0123</v>
       </c>
       <c r="W6" t="n">
-        <v>0.266</v>
+        <v>2.9449</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.139</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>S. NDOUR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6675</v>
+        <v>-1.6105</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5755</v>
+        <v>-0.9154</v>
       </c>
       <c r="F7" t="n">
-        <v>0.908</v>
+        <v>-0.695</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0912</v>
+        <v>1.9564</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.0155</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3397</v>
+        <v>1.9719</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.1156</v>
+        <v>1.9303</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0403</v>
+        <v>0.6452</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.156</v>
+        <v>1.2852</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0244</v>
+        <v>0.026</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.6607</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8162</v>
+        <v>0.6867</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3968</v>
+        <v>-2.7774</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0605</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6744</v>
+        <v>0.0624</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3861</v>
+        <v>0.0212</v>
       </c>
       <c r="V7" t="n">
-        <v>1.881</v>
+        <v>-0.873</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6745</v>
+        <v>-1.139</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9828</v>
+        <v>-1.6603</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1912</v>
+        <v>-2.9247</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2084</v>
+        <v>1.2645</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2059</v>
@@ -1078,13 +1078,13 @@
         <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6541</v>
+        <v>-0.3316</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5611</v>
+        <v>-0.2947</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.093</v>
+        <v>-0.0369</v>
       </c>
       <c r="V8" t="n">
         <v>0.266</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2847</v>
+        <v>-2.2887</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0257</v>
+        <v>-1.8613</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2591</v>
+        <v>-0.4274</v>
       </c>
       <c r="G9" t="n">
         <v>0.6717</v>
@@ -1156,13 +1156,13 @@
         <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.492</v>
+        <v>-0.496</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8105</v>
+        <v>-0.6461</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3184</v>
+        <v>0.1501</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4724</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7395</v>
+        <v>-2.7392</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6293</v>
+        <v>-3.5061</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1102</v>
+        <v>0.7668</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4187</v>
+        <v>-1.7358</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.371</v>
+        <v>-2.2282</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9523</v>
+        <v>0.4924</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3201</v>
+        <v>-2.3385</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3201</v>
+        <v>-1.8591</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.4794</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9014</v>
+        <v>0.6027</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0509</v>
+        <v>-0.369</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9523</v>
+        <v>0.9718</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5871</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-1.1903</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4727</v>
+        <v>-0.0709</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6746</v>
+        <v>0.0228</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2019</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2065</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2065</v>
+        <v>-0.5358000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2862</v>
+        <v>-3.1089</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7725</v>
+        <v>-5.7945</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4863</v>
+        <v>2.6856</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7358</v>
+        <v>-1.5477</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2282</v>
+        <v>-0.7716</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4924</v>
+        <v>-0.7761</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3385</v>
+        <v>-3.6176</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8591</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4794</v>
+        <v>-2.6806</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6027</v>
+        <v>2.0699</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.369</v>
+        <v>0.1653</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9718</v>
+        <v>1.9045</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3968</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6178</v>
+        <v>-0.3076</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2436</v>
+        <v>-0.2607</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3742</v>
+        <v>-0.0469</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5358000000000001</v>
+        <v>0.3334</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5358000000000001</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5309</v>
+        <v>-3.4617</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.469</v>
+        <v>-3.0148</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9381</v>
+        <v>-0.4469</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5477</v>
+        <v>-0.4187</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7716</v>
+        <v>-1.371</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7761</v>
+        <v>0.9523</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.6176</v>
+        <v>-1.3201</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-1.3201</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6806</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0699</v>
+        <v>0.9014</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1653</v>
+        <v>-0.0509</v>
       </c>
       <c r="O12" t="n">
-        <v>1.9045</v>
+        <v>0.9523</v>
       </c>
       <c r="P12" t="n">
         <v>-1.5871</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1822</v>
+        <v>-1.9838</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7296</v>
+        <v>-0.2494</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9352</v>
+        <v>0.2891</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2056</v>
+        <v>-0.5386</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3334</v>
+        <v>-1.2065</v>
       </c>
       <c r="W12" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0675</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.0433</v>
+        <v>-10.1083</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.28</v>
+        <v>-15.3448</v>
       </c>
       <c r="F13" t="n">
-        <v>5.2366</v>
+        <v>5.2367</v>
       </c>
       <c r="G13" t="n">
-        <v>2.089699999999998</v>
+        <v>2.089699999999999</v>
       </c>
       <c r="H13" t="n">
         <v>-7.335600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>7.9355</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.2027</v>
+        <v>-2.2676</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.238</v>
+        <v>-1.303</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9645999999999999</v>
+        <v>-0.9647999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>3.956700000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7974</v>
+        <v>5.3774</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3679</v>
+        <v>3.7557</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4295</v>
+        <v>1.6217</v>
       </c>
       <c r="G14" t="n">
         <v>1.2449</v>
@@ -1546,13 +1546,13 @@
         <v>3.3725</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1088</v>
+        <v>0.6887</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8277</v>
+        <v>0.2156</v>
       </c>
       <c r="U14" t="n">
-        <v>0.281</v>
+        <v>0.4732</v>
       </c>
       <c r="V14" t="n">
         <v>0.0713</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5722</v>
+        <v>4.6266</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6677</v>
+        <v>0.3616</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9045</v>
+        <v>4.265</v>
       </c>
       <c r="G15" t="n">
         <v>3.5613</v>
@@ -1624,13 +1624,13 @@
         <v>3.5709</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8242</v>
+        <v>0.8786</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0148</v>
+        <v>0.7087</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1905</v>
+        <v>0.1699</v>
       </c>
       <c r="V15" t="n">
         <v>-0.4085</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7662</v>
+        <v>3.188</v>
       </c>
       <c r="E16" t="n">
-        <v>1.593</v>
+        <v>0.8788</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1731</v>
+        <v>2.3091</v>
       </c>
       <c r="G16" t="n">
         <v>1.0138</v>
@@ -1702,13 +1702,13 @@
         <v>3.3725</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9669</v>
+        <v>1.3887</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7573</v>
+        <v>1.0431</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2096</v>
+        <v>0.3456</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6032</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5938</v>
+        <v>1.1967</v>
       </c>
       <c r="E17" t="n">
         <v>-1.7295</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3232</v>
+        <v>2.9262</v>
       </c>
       <c r="G17" t="n">
         <v>0.3054</v>
@@ -1780,13 +1780,13 @@
         <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6932</v>
+        <v>0.2961</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0679</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7611</v>
+        <v>0.3641</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4988</v>
+        <v>0.9122</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.2569</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9358</v>
+        <v>0.6553</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6025</v>
@@ -1858,13 +1858,13 @@
         <v>3.1741</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4114</v>
+        <v>0.8247</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1475</v>
+        <v>-0.1586</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2639</v>
+        <v>0.9833</v>
       </c>
       <c r="V18" t="n">
         <v>-2.4842</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1244</v>
+        <v>0.4521</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7468</v>
+        <v>-0.3387</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.2046</v>
@@ -1936,13 +1936,13 @@
         <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7096</v>
+        <v>-0.1332</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3797</v>
+        <v>0.0284</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3299</v>
+        <v>-0.1616</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2065</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. LOPEZ SAURA</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5094</v>
+        <v>0.2209</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1045</v>
+        <v>-2.4781</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4048</v>
+        <v>2.6989</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5831</v>
+        <v>-1.525</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1815</v>
+        <v>2.2776</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4016</v>
+        <v>-3.8026</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0202</v>
+        <v>-2.7049</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0202</v>
+        <v>2.0565</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-4.7614</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6032</v>
+        <v>1.1799</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2016</v>
+        <v>0.2212</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4016</v>
+        <v>0.9588</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1247</v>
+        <v>0.1587</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1247</v>
+        <v>0.2268</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>M. LOPEZ SAURA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3402</v>
+        <v>-0.5094</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7024</v>
+        <v>-0.1045</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3622</v>
+        <v>-0.4048</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.525</v>
+        <v>-0.5831</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2776</v>
+        <v>-0.1815</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.8026</v>
+        <v>-0.4016</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.7049</v>
+        <v>0.0202</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0565</v>
+        <v>0.0202</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.7614</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1799</v>
+        <v>-0.6032</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2212</v>
+        <v>-0.2016</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9588</v>
+        <v>-0.4016</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4023</v>
+        <v>-0.1247</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.1247</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4048</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6276</v>
+        <v>-1.3573</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8128</v>
+        <v>-0.7108</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8148</v>
+        <v>-0.6465</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9585</v>
@@ -2170,13 +2170,13 @@
         <v>0.1984</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3355</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3741</v>
+        <v>-0.272</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0385</v>
+        <v>0.2069</v>
       </c>
       <c r="V22" t="n">
         <v>-0.532</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5835</v>
+        <v>-2.3836</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3322</v>
+        <v>-5.1281</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7487</v>
+        <v>2.7445</v>
       </c>
       <c r="G23" t="n">
         <v>-4.7507</v>
@@ -2248,13 +2248,13 @@
         <v>3.1741</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2296</v>
+        <v>-0.0297</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8388</v>
+        <v>-0.6347</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6092</v>
+        <v>0.605</v>
       </c>
       <c r="V23" t="n">
         <v>1.2065</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11.0433</v>
+        <v>11.7236</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2366</v>
+        <v>-5.236699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>16.2799</v>
+        <v>16.9602</v>
       </c>
       <c r="G24" t="n">
         <v>-2.089799999999999</v>
@@ -2326,13 +2326,13 @@
         <v>21.8222</v>
       </c>
       <c r="S24" t="n">
-        <v>3.202799999999999</v>
+        <v>3.8827</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9645999999999999</v>
+        <v>0.9646999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2381</v>
+        <v>2.9183</v>
       </c>
       <c r="V24" t="n">
         <v>-3.9566</v>
